--- a/sprint_tasks_template_short.xlsx
+++ b/sprint_tasks_template_short.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Desktop\git\langchain\srpint_ai_agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAFE1DE-9E2B-44E6-A8A8-C1F673D7EA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726FB447-E2FE-4DEB-B503-85E2AA10E9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2620" yWindow="4940" windowWidth="28800" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="95">
   <si>
     <t>task_id</t>
   </si>
@@ -230,9 +230,6 @@
     <t>SA-201</t>
   </si>
   <si>
-    <t>Системный анализ магистрального проекта</t>
-  </si>
-  <si>
     <t>Как команда разработки мы хотим иметь готовый системный анализ.</t>
   </si>
   <si>
@@ -405,6 +402,21 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>SA-20221</t>
+  </si>
+  <si>
+    <t>Как команда разработки мы хотим иметь готовый отчет по оборудованию.</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Системный анализ магистрального проекта L12 </t>
   </si>
 </sst>
 </file>
@@ -865,10 +877,10 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -906,7 +918,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M2" s="4">
         <v>2</v>
@@ -918,7 +930,7 @@
         <v>8000</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -935,7 +947,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>28</v>
@@ -956,19 +968,19 @@
         <v>9</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M3" s="4">
         <v>0</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O3" s="5">
         <v>3000</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -976,16 +988,16 @@
         <v>31</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>28</v>
@@ -994,10 +1006,10 @@
         <v>20</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="J4" s="5">
         <v>15</v>
@@ -1006,33 +1018,33 @@
         <v>8</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M4" s="4">
         <v>0</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O4" s="5">
         <v>2500</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>27</v>
@@ -1044,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>30</v>
@@ -1056,33 +1068,33 @@
         <v>9</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M5" s="4">
         <v>2</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O5" s="5">
         <v>5000</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>27</v>
@@ -1094,10 +1106,10 @@
         <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="J6" s="5">
         <v>13</v>
@@ -1106,33 +1118,33 @@
         <v>5</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M6" s="4">
         <v>1</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O6" s="5">
         <v>12000</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>18</v>
@@ -1144,7 +1156,7 @@
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>22</v>
@@ -1156,27 +1168,27 @@
         <v>10</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M7" s="4">
         <v>2</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O7" s="5">
         <v>3000</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>26</v>
@@ -1185,19 +1197,19 @@
         <v>17</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J8" s="5">
         <v>3</v>
@@ -1206,30 +1218,30 @@
         <v>9</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M8" s="4">
         <v>3</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O8" s="5">
         <v>800</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>17</v>
@@ -1238,16 +1250,16 @@
         <v>27</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="J9" s="5">
         <v>5</v>
@@ -1256,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M9" s="4">
         <v>0</v>
@@ -1266,21 +1278,21 @@
         <v>2500</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>18</v>
@@ -1289,13 +1301,13 @@
         <v>28</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J10" s="5">
         <v>34</v>
@@ -1304,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M10" s="4">
         <v>0</v>
@@ -1314,25 +1326,58 @@
         <v>3000</v>
       </c>
       <c r="P10" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="5"/>
+      <c r="F11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="5">
+        <v>12</v>
+      </c>
+      <c r="K11" s="6">
+        <v>8</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
@@ -2870,7 +2915,8 @@
   </sheetData>
   <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2885,79 +2931,79 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
         <v>44</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
         <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
         <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
         <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
         <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
         <v>56</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
         <v>58</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
         <v>60</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/sprint_tasks_template_short.xlsx
+++ b/sprint_tasks_template_short.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Desktop\git\langchain\srpint_ai_agent\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaluzhinanton/Desktop/git/ai-sprint-planner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726FB447-E2FE-4DEB-B503-85E2AA10E9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BE705E-E144-9240-80D5-D95516E0DCAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="4940" windowWidth="28800" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2620" yWindow="4920" windowWidth="28800" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
     <sheet name="instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tasks!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tasks!$A$1:$P$22</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="142">
   <si>
     <t>task_id</t>
   </si>
@@ -413,10 +413,151 @@
     <t>Как команда разработки мы хотим иметь готовый отчет по оборудованию.</t>
   </si>
   <si>
-    <t>Системный анализ магистрального проекта ЦД</t>
-  </si>
-  <si>
     <t xml:space="preserve">Системный анализ магистрального проекта L12 </t>
+  </si>
+  <si>
+    <t>SA-20222</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L1</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L2</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L3</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L4</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L5</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L6</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L7</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L8</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L9</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L10</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L11</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L12</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L13</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L14</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L15</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L16</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L17</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L18</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L19</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L20</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L21</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L22</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L23</t>
+  </si>
+  <si>
+    <t>Системный анализ магистрального проекта ЦД. L24</t>
+  </si>
+  <si>
+    <t>SA-20223</t>
+  </si>
+  <si>
+    <t>SA-20224</t>
+  </si>
+  <si>
+    <t>SA-20225</t>
+  </si>
+  <si>
+    <t>SA-20226</t>
+  </si>
+  <si>
+    <t>SA-20227</t>
+  </si>
+  <si>
+    <t>SA-20228</t>
+  </si>
+  <si>
+    <t>SA-20229</t>
+  </si>
+  <si>
+    <t>SA-20230</t>
+  </si>
+  <si>
+    <t>SA-20231</t>
+  </si>
+  <si>
+    <t>SA-20232</t>
+  </si>
+  <si>
+    <t>SA-20233</t>
+  </si>
+  <si>
+    <t>SA-20234</t>
+  </si>
+  <si>
+    <t>SA-20235</t>
+  </si>
+  <si>
+    <t>SA-20236</t>
+  </si>
+  <si>
+    <t>SA-20237</t>
+  </si>
+  <si>
+    <t>SA-20238</t>
+  </si>
+  <si>
+    <t>SA-20239</t>
+  </si>
+  <si>
+    <t>SA-20240</t>
+  </si>
+  <si>
+    <t>SA-20241</t>
+  </si>
+  <si>
+    <t>SA-20242</t>
+  </si>
+  <si>
+    <t>SA-20243</t>
+  </si>
+  <si>
+    <t>SA-20244</t>
   </si>
 </sst>
 </file>
@@ -426,7 +567,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,15 +580,23 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -494,7 +643,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -511,8 +660,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Normal" xfId="1" xr:uid="{2F0F9255-9010-4CCD-8C69-465CAE1C0985}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -813,9 +962,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="7" customWidth="1"/>
     <col min="3" max="3" width="48" style="7" customWidth="1"/>
     <col min="4" max="4" width="10" style="7" customWidth="1"/>
@@ -826,14 +975,14 @@
     <col min="9" max="9" width="24" style="7" customWidth="1"/>
     <col min="10" max="10" width="8" style="7" customWidth="1"/>
     <col min="11" max="11" width="14" style="7" customWidth="1"/>
-    <col min="12" max="12" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.90625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" style="7" customWidth="1"/>
     <col min="14" max="14" width="45" style="7" customWidth="1"/>
     <col min="15" max="15" width="12" style="7" customWidth="1"/>
-    <col min="16" max="16" width="8.7265625" style="7"/>
+    <col min="16" max="16" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -883,7 +1032,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -933,7 +1082,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
@@ -983,12 +1132,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>32</v>
@@ -1033,7 +1182,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>36</v>
       </c>
@@ -1083,7 +1232,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>62</v>
       </c>
@@ -1112,7 +1261,7 @@
         <v>65</v>
       </c>
       <c r="J6" s="5">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K6" s="6">
         <v>5</v>
@@ -1133,7 +1282,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>67</v>
       </c>
@@ -1183,7 +1332,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>72</v>
       </c>
@@ -1233,7 +1382,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -1281,7 +1430,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>82</v>
       </c>
@@ -1310,7 +1459,7 @@
         <v>85</v>
       </c>
       <c r="J10" s="5">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K10" s="6">
         <v>10</v>
@@ -1325,16 +1474,16 @@
       <c r="O10" s="5">
         <v>3000</v>
       </c>
-      <c r="P10" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="P10" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>92</v>
@@ -1375,405 +1524,1078 @@
       <c r="O11" s="5">
         <v>2500</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="P11" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="5">
+        <v>12</v>
+      </c>
+      <c r="K12" s="6">
+        <v>8</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" s="5">
+        <v>12</v>
+      </c>
+      <c r="K13" s="6">
+        <v>8</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="5">
+        <v>12</v>
+      </c>
+      <c r="K14" s="6">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J15" s="5">
+        <v>34</v>
+      </c>
+      <c r="K15" s="6">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J16" s="5">
+        <v>8</v>
+      </c>
+      <c r="K16" s="6">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J17" s="5">
+        <v>8</v>
+      </c>
+      <c r="K17" s="6">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" s="5">
+        <v>2</v>
+      </c>
+      <c r="K18" s="6">
+        <v>8</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O18" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J19" s="5">
+        <v>2</v>
+      </c>
+      <c r="K19" s="6">
+        <v>8</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O19" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J20" s="5">
+        <v>3</v>
+      </c>
+      <c r="K20" s="6">
+        <v>8</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O20" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="4"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="4"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
+    <row r="21" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J21" s="5">
+        <v>2</v>
+      </c>
+      <c r="K21" s="6">
+        <v>8</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" s="4">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O21" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="6">
+        <v>8</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="4">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O22" s="5">
+        <v>2500</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1</v>
+      </c>
+      <c r="K23" s="6">
+        <v>8</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" s="4">
+        <v>1</v>
+      </c>
       <c r="N23" s="4"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
+    <row r="24" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" s="5">
+        <v>1</v>
+      </c>
+      <c r="K24" s="6">
+        <v>8</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" s="4">
+        <v>2</v>
+      </c>
       <c r="N24" s="4"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
+    <row r="25" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1</v>
+      </c>
+      <c r="K25" s="6">
+        <v>8</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M25" s="4">
+        <v>3</v>
+      </c>
       <c r="N25" s="4"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
+    <row r="26" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1</v>
+      </c>
+      <c r="K26" s="6">
+        <v>8</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M26" s="4">
+        <v>4</v>
+      </c>
       <c r="N26" s="4"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
+    <row r="27" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1</v>
+      </c>
+      <c r="K27" s="6">
+        <v>8</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M27" s="4">
+        <v>5</v>
+      </c>
       <c r="N27" s="4"/>
       <c r="O27" s="5"/>
       <c r="P27" s="4"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
+    <row r="28" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="6">
+        <v>8</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M28" s="4">
+        <v>6</v>
+      </c>
       <c r="N28" s="4"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
+    <row r="29" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+      <c r="K29" s="6">
+        <v>8</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M29" s="4">
+        <v>7</v>
+      </c>
       <c r="N29" s="4"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
+    <row r="30" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J30" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K30" s="6">
+        <v>8</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M30" s="4">
+        <v>8</v>
+      </c>
       <c r="N30" s="4"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
+    <row r="31" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K31" s="6">
+        <v>8</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M31" s="4">
+        <v>9</v>
+      </c>
       <c r="N31" s="4"/>
       <c r="O31" s="5"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
+    <row r="32" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J32" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K32" s="6">
+        <v>8</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M32" s="4">
+        <v>10</v>
+      </c>
       <c r="N32" s="4"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
+    <row r="33" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K33" s="6">
+        <v>8</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M33" s="4">
+        <v>11</v>
+      </c>
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
+    <row r="34" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K34" s="6">
+        <v>8</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M34" s="4">
+        <v>12</v>
+      </c>
       <c r="N34" s="4"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1790,7 +2612,7 @@
       <c r="N35" s="4"/>
       <c r="O35" s="5"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1807,7 +2629,7 @@
       <c r="N36" s="4"/>
       <c r="O36" s="5"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1824,7 +2646,7 @@
       <c r="N37" s="4"/>
       <c r="O37" s="5"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1841,7 +2663,7 @@
       <c r="N38" s="4"/>
       <c r="O38" s="5"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1858,7 +2680,7 @@
       <c r="N39" s="4"/>
       <c r="O39" s="5"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1875,7 +2697,7 @@
       <c r="N40" s="4"/>
       <c r="O40" s="5"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1892,7 +2714,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1909,7 +2731,7 @@
       <c r="N42" s="4"/>
       <c r="O42" s="5"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1926,7 +2748,7 @@
       <c r="N43" s="4"/>
       <c r="O43" s="5"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1943,7 +2765,7 @@
       <c r="N44" s="4"/>
       <c r="O44" s="5"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1960,7 +2782,7 @@
       <c r="N45" s="4"/>
       <c r="O45" s="5"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1977,7 +2799,7 @@
       <c r="N46" s="4"/>
       <c r="O46" s="5"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1994,7 +2816,7 @@
       <c r="N47" s="4"/>
       <c r="O47" s="5"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2011,7 +2833,7 @@
       <c r="N48" s="4"/>
       <c r="O48" s="5"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2028,7 +2850,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2045,7 +2867,7 @@
       <c r="N50" s="4"/>
       <c r="O50" s="5"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -2062,7 +2884,7 @@
       <c r="N51" s="4"/>
       <c r="O51" s="5"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2079,7 +2901,7 @@
       <c r="N52" s="4"/>
       <c r="O52" s="5"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2096,7 +2918,7 @@
       <c r="N53" s="4"/>
       <c r="O53" s="5"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2113,7 +2935,7 @@
       <c r="N54" s="4"/>
       <c r="O54" s="5"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2130,7 +2952,7 @@
       <c r="N55" s="4"/>
       <c r="O55" s="5"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2147,7 +2969,7 @@
       <c r="N56" s="4"/>
       <c r="O56" s="5"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2164,7 +2986,7 @@
       <c r="N57" s="4"/>
       <c r="O57" s="5"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2181,7 +3003,7 @@
       <c r="N58" s="4"/>
       <c r="O58" s="5"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2198,7 +3020,7 @@
       <c r="N59" s="4"/>
       <c r="O59" s="5"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2215,7 +3037,7 @@
       <c r="N60" s="4"/>
       <c r="O60" s="5"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2232,7 +3054,7 @@
       <c r="N61" s="4"/>
       <c r="O61" s="5"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2249,7 +3071,7 @@
       <c r="N62" s="4"/>
       <c r="O62" s="5"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2266,7 +3088,7 @@
       <c r="N63" s="4"/>
       <c r="O63" s="5"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2283,7 +3105,7 @@
       <c r="N64" s="4"/>
       <c r="O64" s="5"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2300,7 +3122,7 @@
       <c r="N65" s="4"/>
       <c r="O65" s="5"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2317,7 +3139,7 @@
       <c r="N66" s="4"/>
       <c r="O66" s="5"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2334,7 +3156,7 @@
       <c r="N67" s="4"/>
       <c r="O67" s="5"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2351,7 +3173,7 @@
       <c r="N68" s="4"/>
       <c r="O68" s="5"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2368,7 +3190,7 @@
       <c r="N69" s="4"/>
       <c r="O69" s="5"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2385,7 +3207,7 @@
       <c r="N70" s="4"/>
       <c r="O70" s="5"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2402,7 +3224,7 @@
       <c r="N71" s="4"/>
       <c r="O71" s="5"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2419,7 +3241,7 @@
       <c r="N72" s="4"/>
       <c r="O72" s="5"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2436,7 +3258,7 @@
       <c r="N73" s="4"/>
       <c r="O73" s="5"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2453,7 +3275,7 @@
       <c r="N74" s="4"/>
       <c r="O74" s="5"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2470,7 +3292,7 @@
       <c r="N75" s="4"/>
       <c r="O75" s="5"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2487,7 +3309,7 @@
       <c r="N76" s="4"/>
       <c r="O76" s="5"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2504,7 +3326,7 @@
       <c r="N77" s="4"/>
       <c r="O77" s="5"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2521,7 +3343,7 @@
       <c r="N78" s="4"/>
       <c r="O78" s="5"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2538,7 +3360,7 @@
       <c r="N79" s="4"/>
       <c r="O79" s="5"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2555,7 +3377,7 @@
       <c r="N80" s="4"/>
       <c r="O80" s="5"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2572,7 +3394,7 @@
       <c r="N81" s="4"/>
       <c r="O81" s="5"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2589,7 +3411,7 @@
       <c r="N82" s="4"/>
       <c r="O82" s="5"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2606,7 +3428,7 @@
       <c r="N83" s="4"/>
       <c r="O83" s="5"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2623,7 +3445,7 @@
       <c r="N84" s="4"/>
       <c r="O84" s="5"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2640,7 +3462,7 @@
       <c r="N85" s="4"/>
       <c r="O85" s="5"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2657,7 +3479,7 @@
       <c r="N86" s="4"/>
       <c r="O86" s="5"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2674,7 +3496,7 @@
       <c r="N87" s="4"/>
       <c r="O87" s="5"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2691,7 +3513,7 @@
       <c r="N88" s="4"/>
       <c r="O88" s="5"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2708,7 +3530,7 @@
       <c r="N89" s="4"/>
       <c r="O89" s="5"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2725,7 +3547,7 @@
       <c r="N90" s="4"/>
       <c r="O90" s="5"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2742,7 +3564,7 @@
       <c r="N91" s="4"/>
       <c r="O91" s="5"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2759,7 +3581,7 @@
       <c r="N92" s="4"/>
       <c r="O92" s="5"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -2776,7 +3598,7 @@
       <c r="N93" s="4"/>
       <c r="O93" s="5"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -2793,7 +3615,7 @@
       <c r="N94" s="4"/>
       <c r="O94" s="5"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -2810,7 +3632,7 @@
       <c r="N95" s="4"/>
       <c r="O95" s="5"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -2827,7 +3649,7 @@
       <c r="N96" s="4"/>
       <c r="O96" s="5"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -2844,7 +3666,7 @@
       <c r="N97" s="4"/>
       <c r="O97" s="5"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -2861,7 +3683,7 @@
       <c r="N98" s="4"/>
       <c r="O98" s="5"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -2878,7 +3700,7 @@
       <c r="N99" s="4"/>
       <c r="O99" s="5"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -2895,7 +3717,7 @@
       <c r="N100" s="4"/>
       <c r="O100" s="5"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -2913,7 +3735,8 @@
       <c r="O101" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P22" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -2923,18 +3746,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -2942,7 +3765,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -2950,7 +3773,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -2958,7 +3781,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -2966,7 +3789,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -2974,7 +3797,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2982,7 +3805,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -2990,7 +3813,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -2998,7 +3821,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>59</v>
       </c>
